--- a/Outputs/Scenarios/PtX_demand_FR_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_FR_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.006379959808676661</v>
       </c>
       <c r="K16" t="n">
-        <v>0.006320500214814401</v>
+        <v>0.007716057101498001</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01053416702469067</v>
+        <v>0.009346593863518333</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>9.192442138230554e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.004213666809876268</v>
+        <v>0.004005683084365001</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.009444753759612115</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03382513997362098</v>
+        <v>0.04129367971396962</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0563752332893683</v>
+        <v>0.05001975080533688</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.0004970923031374797</v>
       </c>
       <c r="K42" t="n">
-        <v>0.02255009331574732</v>
+        <v>0.02143703605943009</v>
       </c>
     </row>
     <row r="43">
